--- a/w5-zone3-consumption-gating/poc07-nb/POC07_CTAS_Swap_Test_Tracker.xlsx
+++ b/w5-zone3-consumption-gating/poc07-nb/POC07_CTAS_Swap_Test_Tracker.xlsx
@@ -4357,7 +4357,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00228D31-08DB-4320-B2D6-4CC30B3DABA3}">
-  <dimension ref="A1:C321"/>
+  <dimension ref="A1:C324"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="60.42578125" customWidth="1"/>
@@ -4385,6 +4385,23 @@
         <v>105</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Shot 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TC-01.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tags on NB_D_STAGE.CUSTOMER_360 after the FIRST CTAS with COPY TAGS - expected ZERO PII rows because there is no predecessor table to copy from; got 'Query produced no results'. PASS - tag bootstrap gap confirmed on a real account.</t>
+        </is>
+      </c>
+    </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>96</v>
@@ -4407,6 +4424,57 @@
         <v>109</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Shot 2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TC-01.2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security gate sec-1 re-reads those tags before publishing - expected ZERO rows so the gate refuses the batch; got no results. PASS - the gate correctly blocks an untagged build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Shot 3</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TC-01.2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unentitled reader reads the untagged staging table directly - expected REAL e-mail and SSN because an untagged column has nothing to mask it; got cust1@example.invalid / 001-00-0000. PASS - this is the exposure the gate exists to prevent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Shot 4</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>TC-01.2</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publish REFUSED and logged, then the thin reader views are checked - expected them still empty because no swap happened; got distinct_batches = 0, batch_seen = null. PASS (the script's EXPECT line said 1 - a documentation defect, now corrected).</t>
+        </is>
+      </c>
+    </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>96</v>
@@ -4429,6 +4497,23 @@
         <v>113</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Shot 5</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TC-01.3</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PII tags applied to CUSTOMER_360 in BOTH NB_D_LIVE and NB_D_STAGE, then rebuilt - expected 2 rows, email=EMAIL and ssn=SSN; got exactly that. PASS - seeding both schemas is the fix.</t>
+        </is>
+      </c>
+    </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>96</v>
@@ -4451,6 +4536,91 @@
         <v>117</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Shot 6</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>TC-01.4</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security gate sec-1 re-run after the fix - expected 2 rows; got 2. PASS - the gate now lets the batch through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Shot 7</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>TC-01.4</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unentitled reader reads staging after tagging - expected ***MASKED***; got ***MASKED*** in both columns. PASS - this also closes setup assertion 6c: the masking policy really is driven by the tag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Shot 8</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>TC-01.4</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After ALTER SCHEMA SWAP, batch ids across both thin reader views - expected distinct_batches = 1 and batch_seen = B1; got 1 / B1. PASS - the publish is atomic and the views are internally consistent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Shot 9</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>TC-01.4</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approved reader NB_READER_OK through the thin view - expected real values; got cust1@example.invalid / 001-00-0000. PASS - entitlement works end to end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Shot 10</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TC-01.4</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unapproved reader NB_READER_NO through the same thin view - expected ***MASKED***; got ***MASKED***. PASS - masking survives the schema swap.</t>
+        </is>
+      </c>
+    </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
         <v>96</v>
@@ -4473,6 +4643,57 @@
         <v>122</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Shot 11</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>TC-01.5</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch B2 builds into the OTHER storage, the one that was NB_D_LIVE before the swap - expected 2 rows, and ZERO would have meant only one schema was seeded; got 2. PASS - this is the check that proves the swap-pair alternation is defeated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Shot 12</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>TC-01.5</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security gate sec-1 on batch B2 - expected 2 rows; got 2. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Shot 13</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>TC-01.5</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unentitled read of staging before the B2 swap - expected ***MASKED***; got ***MASKED***. PASS - the second storage is protected too.</t>
+        </is>
+      </c>
+    </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
         <v>96</v>
@@ -4493,6 +4714,23 @@
       </c>
       <c r="C321" s="5" t="s">
         <v>126</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Shot 14</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>TC-01.6</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After the second swap, batch ids across every thin reader view - expected distinct_batches = 1 and batch_seen = B2; got 1 / B2. PASS - no mixed-batch read, which is the entire requirement.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/w5-zone3-consumption-gating/poc07-nb/POC07_CTAS_Swap_Test_Tracker.xlsx
+++ b/w5-zone3-consumption-gating/poc07-nb/POC07_CTAS_Swap_Test_Tracker.xlsx
@@ -8,27 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikhilbansal5\Desktop\Client_project\Liberty Mutual\Design\tagging_keys_persistence_zone3\claude\evidence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EABA16-DCB2-4099-A2E4-632A0B1DF66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AB1675-5B2D-4171-84A2-4CB552332BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_Flow" sheetId="1" r:id="rId1"/>
     <sheet name="2_Scenarios" sheetId="3" r:id="rId2"/>
-    <sheet name="3_Test_Cases" sheetId="4" r:id="rId3"/>
-    <sheet name="5_Control_Tables" sheetId="5" r:id="rId4"/>
+    <sheet name="5_Control_Tables" sheetId="5" r:id="rId3"/>
+    <sheet name="3_Test_Cases" sheetId="4" r:id="rId4"/>
     <sheet name="S01" sheetId="7" r:id="rId5"/>
+    <sheet name="S02" sheetId="8" r:id="rId6"/>
+    <sheet name="S03" sheetId="9" r:id="rId7"/>
+    <sheet name="S04" sheetId="10" r:id="rId8"/>
+    <sheet name="S05" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_Scenarios'!$B$4:$H$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3_Test_Cases'!$B$4:$I$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3_Test_Cases'!$B$4:$I$52</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="357">
   <si>
     <t>Zone 3 consumption gating — CTAS + Swap</t>
   </si>
@@ -1024,6 +1028,90 @@
   </si>
   <si>
     <t xml:space="preserve">  AND NVL(s.exception_flag,'N') &lt;&gt; 'Y';</t>
+  </si>
+  <si>
+    <t>Shot 1</t>
+  </si>
+  <si>
+    <t>Tags on NB_D_STAGE.CUSTOMER_360 after the FIRST CTAS with COPY TAGS - expected ZERO PII rows because there is no predecessor table to copy from; got 'Query produced no results'. PASS - tag bootstrap gap confirmed on a real account.</t>
+  </si>
+  <si>
+    <t>Shot 2</t>
+  </si>
+  <si>
+    <t>Security gate sec-1 re-reads those tags before publishing - expected ZERO rows so the gate refuses the batch; got no results. PASS - the gate correctly blocks an untagged build.</t>
+  </si>
+  <si>
+    <t>Shot 3</t>
+  </si>
+  <si>
+    <t>Unentitled reader reads the untagged staging table directly - expected REAL e-mail and SSN because an untagged column has nothing to mask it; got cust1@example.invalid / 001-00-0000. PASS - this is the exposure the gate exists to prevent.</t>
+  </si>
+  <si>
+    <t>Shot 4</t>
+  </si>
+  <si>
+    <t>Publish REFUSED and logged, then the thin reader views are checked - expected them still empty because no swap happened; got distinct_batches = 0, batch_seen = null. PASS (the script's EXPECT line said 1 - a documentation defect, now corrected).</t>
+  </si>
+  <si>
+    <t>Shot 5</t>
+  </si>
+  <si>
+    <t>PII tags applied to CUSTOMER_360 in BOTH NB_D_LIVE and NB_D_STAGE, then rebuilt - expected 2 rows, email=EMAIL and ssn=SSN; got exactly that. PASS - seeding both schemas is the fix.</t>
+  </si>
+  <si>
+    <t>Shot 6</t>
+  </si>
+  <si>
+    <t>Security gate sec-1 re-run after the fix - expected 2 rows; got 2. PASS - the gate now lets the batch through.</t>
+  </si>
+  <si>
+    <t>Shot 7</t>
+  </si>
+  <si>
+    <t>Unentitled reader reads staging after tagging - expected ***MASKED***; got ***MASKED*** in both columns. PASS - this also closes setup assertion 6c: the masking policy really is driven by the tag.</t>
+  </si>
+  <si>
+    <t>Shot 8</t>
+  </si>
+  <si>
+    <t>After ALTER SCHEMA SWAP, batch ids across both thin reader views - expected distinct_batches = 1 and batch_seen = B1; got 1 / B1. PASS - the publish is atomic and the views are internally consistent.</t>
+  </si>
+  <si>
+    <t>Shot 9</t>
+  </si>
+  <si>
+    <t>Approved reader NB_READER_OK through the thin view - expected real values; got cust1@example.invalid / 001-00-0000. PASS - entitlement works end to end.</t>
+  </si>
+  <si>
+    <t>Shot 10</t>
+  </si>
+  <si>
+    <t>Unapproved reader NB_READER_NO through the same thin view - expected ***MASKED***; got ***MASKED***. PASS - masking survives the schema swap.</t>
+  </si>
+  <si>
+    <t>Shot 11</t>
+  </si>
+  <si>
+    <t>Batch B2 builds into the OTHER storage, the one that was NB_D_LIVE before the swap - expected 2 rows, and ZERO would have meant only one schema was seeded; got 2. PASS - this is the check that proves the swap-pair alternation is defeated.</t>
+  </si>
+  <si>
+    <t>Shot 12</t>
+  </si>
+  <si>
+    <t>Security gate sec-1 on batch B2 - expected 2 rows; got 2. PASS.</t>
+  </si>
+  <si>
+    <t>Shot 13</t>
+  </si>
+  <si>
+    <t>Unentitled read of staging before the B2 swap - expected ***MASKED***; got ***MASKED***. PASS - the second storage is protected too.</t>
+  </si>
+  <si>
+    <t>Shot 14</t>
+  </si>
+  <si>
+    <t>After the second swap, batch ids across every thin reader view - expected distinct_batches = 1 and batch_seen = B2; got 1 / B2. PASS - no mixed-batch read, which is the entire requirement.</t>
   </si>
 </sst>
 </file>
@@ -1279,10 +1367,26 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1292,26 +1396,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1950,6 +2038,2710 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>29946</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>10510</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD05D68B-BF2C-4BD1-51B0-F78CD5021D02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="904875"/>
+          <a:ext cx="9821646" cy="7059010"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>592510</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>86508</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBAE9BFF-0D54-AA76-FC70-A1D37D4D59AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="8524875"/>
+          <a:ext cx="14041810" cy="5611008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>468667</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>181373</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4B678D0-271A-138B-A08D-9DB17541F880}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="14620875"/>
+          <a:ext cx="13917967" cy="2848373"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>420865</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>48084</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22C5FBA2-5309-14B0-90A6-23B83F602EE1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="18240375"/>
+          <a:ext cx="12650965" cy="3286584"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>354351</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>171899</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6830BB49-C81A-1142-320F-A7485B1EA103}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="22240875"/>
+          <a:ext cx="13803651" cy="3219899"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>602036</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>57557</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A242EABC-6CF5-E210-8E14-67739CA7BED9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="26241375"/>
+          <a:ext cx="14051336" cy="2915057"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>29946</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>124826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5571418-587C-651E-2778-372B2E40DC88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="30632400"/>
+          <a:ext cx="9821646" cy="7173326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>201</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>516299</xdr:colOff>
+      <xdr:row>230</xdr:row>
+      <xdr:rowOff>76982</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{792A0197-924B-0238-C026-ACA13E607C1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="38442900"/>
+          <a:ext cx="13965599" cy="5601482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>234</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>297278</xdr:colOff>
+      <xdr:row>247</xdr:row>
+      <xdr:rowOff>162293</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{508F1994-572A-8214-3A43-75C34AF7D672}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="44729400"/>
+          <a:ext cx="14356178" cy="2638793"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>252</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>373234</xdr:colOff>
+      <xdr:row>270</xdr:row>
+      <xdr:rowOff>479</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95A3B5D5-A262-BEB8-0491-F01FDE2D6899}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="48158400"/>
+          <a:ext cx="12603334" cy="3429479"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>273</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>497246</xdr:colOff>
+      <xdr:row>290</xdr:row>
+      <xdr:rowOff>9978</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5BBAD40-284E-DACE-A83C-E834EE6F8CF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="52158900"/>
+          <a:ext cx="13946546" cy="3248478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>294</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>602036</xdr:colOff>
+      <xdr:row>309</xdr:row>
+      <xdr:rowOff>143294</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA16F9CD-2659-B402-E322-86B776373993}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="56159400"/>
+          <a:ext cx="14051336" cy="3000794"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>316</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>544197</xdr:colOff>
+      <xdr:row>353</xdr:row>
+      <xdr:rowOff>48615</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E77766D1-0DB3-502C-CEBC-95C0578BA6EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="60359925"/>
+          <a:ext cx="9116697" cy="7097115"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>357</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>144857</xdr:colOff>
+      <xdr:row>386</xdr:row>
+      <xdr:rowOff>153192</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCA7D9DB-5579-A123-9104-43A90F459D52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="68170425"/>
+          <a:ext cx="14203757" cy="5677692"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>390</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>335384</xdr:colOff>
+      <xdr:row>403</xdr:row>
+      <xdr:rowOff>124188</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADBA3A97-5AE9-68E0-3201-34D4DD47574C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="74456925"/>
+          <a:ext cx="14394284" cy="2600688"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>408</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>144602</xdr:colOff>
+      <xdr:row>424</xdr:row>
+      <xdr:rowOff>152847</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C13FD4C4-99DB-4696-9CF4-3AED39B98D22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="77885925"/>
+          <a:ext cx="12374702" cy="3200847"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>428</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>373404</xdr:colOff>
+      <xdr:row>444</xdr:row>
+      <xdr:rowOff>105215</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2EA561-FDAC-EF15-49A8-D8126613E25B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="81695925"/>
+          <a:ext cx="13822704" cy="3153215"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>448</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>344825</xdr:colOff>
+      <xdr:row>463</xdr:row>
+      <xdr:rowOff>86136</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2602922-76E4-865B-5DC1-73A832487194}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="85505925"/>
+          <a:ext cx="13794125" cy="2943636"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>470</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>220387</xdr:colOff>
+      <xdr:row>507</xdr:row>
+      <xdr:rowOff>124826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE2B5194-CD81-A358-6469-D2BDABE40A92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="89706450"/>
+          <a:ext cx="9402487" cy="7173326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>512</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>383015</xdr:colOff>
+      <xdr:row>542</xdr:row>
+      <xdr:rowOff>38903</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8334C442-F527-8BC5-A311-4F29C802BFC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="97707450"/>
+          <a:ext cx="14441915" cy="5753903"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>546</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>582983</xdr:colOff>
+      <xdr:row>559</xdr:row>
+      <xdr:rowOff>143241</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C946F18-5E49-A5E6-7C50-1CF11DB4F9B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="104184450"/>
+          <a:ext cx="14032283" cy="2619741"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>563</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>382845</xdr:colOff>
+      <xdr:row>580</xdr:row>
+      <xdr:rowOff>38557</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E87EEEA-F79A-9E19-4D08-1B19B3CD9D0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="107422950"/>
+          <a:ext cx="13222545" cy="3277057"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>584</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>297193</xdr:colOff>
+      <xdr:row>601</xdr:row>
+      <xdr:rowOff>452</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7D185F5-83E3-220A-71A2-F0634253B152}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="111423450"/>
+          <a:ext cx="13746493" cy="3238952"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>604</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>554404</xdr:colOff>
+      <xdr:row>619</xdr:row>
+      <xdr:rowOff>171873</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Picture 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D0DE76E-082B-D15A-2F66-B5CC924BD262}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="115233450"/>
+          <a:ext cx="14003704" cy="3029373"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>626</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>106837</xdr:colOff>
+      <xdr:row>641</xdr:row>
+      <xdr:rowOff>28978</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Picture 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90D7C201-852B-87D2-41FE-0D1F54BB94FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="119433975"/>
+          <a:ext cx="14775337" cy="2886478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>644</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>21015</xdr:colOff>
+      <xdr:row>659</xdr:row>
+      <xdr:rowOff>143294</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Picture 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{274CCCB5-A790-BA0B-A1BB-EEBE7532652E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="122862975"/>
+          <a:ext cx="14079915" cy="3000794"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>220371</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>19717</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF98653A-4B9A-C3A1-92A5-29D7457D86ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="1095375"/>
+          <a:ext cx="9288171" cy="4782217"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>487789</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>143427</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BA3C97B-61C0-602D-CB9B-E85A343980E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="6429375"/>
+          <a:ext cx="14432389" cy="3953427"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>306193</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>95901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FE564CD-02A4-8A5E-A28B-F8AE3D76FB5A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="11001375"/>
+          <a:ext cx="9983593" cy="4667901"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>325842</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>162479</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF97584D-CC6F-86AE-725C-8FFF35421918}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="16335375"/>
+          <a:ext cx="14270442" cy="3972479"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>68801</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>479</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34212D11-5858-F7B2-695F-F36DBA464D56}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="20907375"/>
+          <a:ext cx="15232601" cy="3429479"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>401797</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>152767</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5CCC5D4-C968-C4A2-7674-9EFFDBD77A62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="25812750"/>
+          <a:ext cx="12517597" cy="2629267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>135060</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>67163</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F5F748B-0BA8-1C57-4126-B2ECD1FBCDE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="29051250"/>
+          <a:ext cx="12250860" cy="3496163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>544266</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>162905</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{541552BA-CEA4-4629-6945-1E73B06AFF42}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="33823275"/>
+          <a:ext cx="9612066" cy="7020905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>216</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>458444</xdr:colOff>
+      <xdr:row>237</xdr:row>
+      <xdr:rowOff>114874</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5CB92EC-160F-EC14-5A84-8882345C4D60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="41633775"/>
+          <a:ext cx="8916644" cy="4115374"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>244</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>363266</xdr:colOff>
+      <xdr:row>269</xdr:row>
+      <xdr:rowOff>19717</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{622C6467-9029-EAE1-C180-86FE685CAA57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="47110650"/>
+          <a:ext cx="9431066" cy="4782217"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>274</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>154197</xdr:colOff>
+      <xdr:row>287</xdr:row>
+      <xdr:rowOff>114662</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00F1A2E8-2E6A-CDCA-11EA-97BCEAB1B52B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="52825650"/>
+          <a:ext cx="12879597" cy="2591162"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>402004</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>143374</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87187CDC-34A4-5CA1-33BC-C9E2D613D0C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="1095375"/>
+          <a:ext cx="14003704" cy="3572374"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>78194</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>162453</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7531F6D-1420-2B2C-1577-3AB10B7500A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="5286375"/>
+          <a:ext cx="14289494" cy="3781953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>563952</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>67189</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ED0EFCD-7C9A-8DCA-7BE0-6E3F14448A41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="10572750"/>
+          <a:ext cx="14165652" cy="3686689"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>30563</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>114874</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{412D16FE-D78C-258E-EFCD-DA94A5DA3378}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="14954250"/>
+          <a:ext cx="14241863" cy="4115374"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>40089</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>134060</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FD0ABC4-C058-8DE0-AC07-B63B625DEF96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="20431125"/>
+          <a:ext cx="14251389" cy="5087060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>420376</xdr:colOff>
+      <xdr:row>169</xdr:row>
+      <xdr:rowOff>48562</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D203CDC-2775-1936-A304-0DF722AA91B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="26146125"/>
+          <a:ext cx="9145276" cy="6716062"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>173</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>116044</xdr:colOff>
+      <xdr:row>193</xdr:row>
+      <xdr:rowOff>57690</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{442DA09A-E7D6-EF12-D620-D0B614F69BD4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="33575625"/>
+          <a:ext cx="12498544" cy="3867690"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>200</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>106773</xdr:colOff>
+      <xdr:row>228</xdr:row>
+      <xdr:rowOff>162692</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7B500EA-450E-B54B-978C-9235985C8268}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="38862000"/>
+          <a:ext cx="14318073" cy="5496692"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>232</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>211478</xdr:colOff>
+      <xdr:row>250</xdr:row>
+      <xdr:rowOff>181479</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7691DF90-9CA2-DCCE-7581-8F2B04CF1884}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="44958000"/>
+          <a:ext cx="13813178" cy="3610479"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>258</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>59142</xdr:colOff>
+      <xdr:row>278</xdr:row>
+      <xdr:rowOff>133900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BF95D11-BC11-8553-1B31-A93CD2F31C75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="50053875"/>
+          <a:ext cx="14270442" cy="3943900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>285</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>411360</xdr:colOff>
+      <xdr:row>296</xdr:row>
+      <xdr:rowOff>66977</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3B37988-E65A-3F5A-3A0F-E12783AC5944}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="55206900"/>
+          <a:ext cx="12793860" cy="2162477"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>303</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>535373</xdr:colOff>
+      <xdr:row>316</xdr:row>
+      <xdr:rowOff>76556</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53055D07-575A-9114-3683-4AC6BAD5CDB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="58778775"/>
+          <a:ext cx="14137073" cy="2553056"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>582374</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>153192</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8EAF6E9-7231-829B-E007-61429E4B1F73}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="962025"/>
+          <a:ext cx="9669224" cy="5677692"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>173423</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>96061</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9726BC15-2747-AE1F-1776-483CC435647E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="7248525"/>
+          <a:ext cx="14137073" cy="5811061"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>573444</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>152767</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9419EAF-3D51-A724-9FAE-2ABA01323954}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="13725525"/>
+          <a:ext cx="13927494" cy="2629267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>297010</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>86189</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{075B769C-7A13-537E-21D8-F4797DE702E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="17154525"/>
+          <a:ext cx="12431860" cy="3324689"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>535338</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>105694</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{880EBD1C-C321-EF59-8828-5F7C9E4FB141}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="21736050"/>
+          <a:ext cx="13889388" cy="6582694"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>354168</xdr:colOff>
+      <xdr:row>169</xdr:row>
+      <xdr:rowOff>143374</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C699016F-5CD6-9506-00C2-018BCD91F5A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="28975050"/>
+          <a:ext cx="12489018" cy="3572374"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>535338</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>162852</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E353C76B-C42B-706C-7B68-5C6562006A74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="34070925"/>
+          <a:ext cx="13889388" cy="6639852"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>344642</xdr:colOff>
+      <xdr:row>232</xdr:row>
+      <xdr:rowOff>181452</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAC0F7A2-DB2F-154F-A169-D07CCC2A5901}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="41309925"/>
+          <a:ext cx="12479492" cy="3419952"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>239</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>468058</xdr:colOff>
+      <xdr:row>265</xdr:row>
+      <xdr:rowOff>162639</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21A77D34-BA90-0244-4514-823E462B2B98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="45891450"/>
+          <a:ext cx="9554908" cy="5115639"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>270</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>268686</xdr:colOff>
+      <xdr:row>299</xdr:row>
+      <xdr:rowOff>76982</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A58C7803-EB60-CC02-2B8B-52BB596E4BCF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="51796950"/>
+          <a:ext cx="14232336" cy="5601482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>303</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>125791</xdr:colOff>
+      <xdr:row>316</xdr:row>
+      <xdr:rowOff>114662</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B3B31E3-F37A-42FA-3C2B-8B08BF485CC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="58083450"/>
+          <a:ext cx="14089441" cy="2591162"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>320</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>344642</xdr:colOff>
+      <xdr:row>336</xdr:row>
+      <xdr:rowOff>143320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E6FB6DE-7FD5-6C37-5F6F-E74F12280B88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="61321950"/>
+          <a:ext cx="12479492" cy="3191320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2261,11 +5053,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="29"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="37"/>
       <c r="F5" s="3" t="s">
         <v>4</v>
       </c>
@@ -2280,11 +5072,11 @@
       <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="5" t="s">
         <v>9</v>
       </c>
@@ -2296,21 +5088,21 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
     </row>
     <row r="8" spans="2:8" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="5" t="s">
         <v>15</v>
       </c>
@@ -2320,21 +5112,21 @@
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
     </row>
     <row r="10" spans="2:8" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
       <c r="F10" s="8" t="s">
         <v>18</v>
       </c>
@@ -2346,21 +5138,21 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
     </row>
     <row r="12" spans="2:8" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
       <c r="F12" s="5" t="s">
         <v>22</v>
       </c>
@@ -2372,21 +5164,21 @@
       </c>
     </row>
     <row r="13" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
     </row>
     <row r="14" spans="2:8" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="5" t="s">
         <v>26</v>
       </c>
@@ -2398,21 +5190,21 @@
       </c>
     </row>
     <row r="15" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
     </row>
     <row r="16" spans="2:8" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="8" t="s">
         <v>30</v>
       </c>
@@ -2424,21 +5216,21 @@
       </c>
     </row>
     <row r="17" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
     </row>
     <row r="18" spans="2:8" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
       <c r="F18" s="5" t="s">
         <v>35</v>
       </c>
@@ -2448,21 +5240,21 @@
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
     </row>
     <row r="20" spans="2:8" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
       <c r="F20" s="8" t="s">
         <v>39</v>
       </c>
@@ -2472,21 +5264,21 @@
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
     </row>
     <row r="22" spans="2:8" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
       <c r="F22" s="5" t="s">
         <v>42</v>
       </c>
@@ -2501,37 +5293,37 @@
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="37" t="s">
+      <c r="B27" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="11" t="s">
@@ -2539,40 +5331,48 @@
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="36" t="s">
+      <c r="B31" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="36" t="s">
+      <c r="B32" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C5:E5"/>
     <mergeCell ref="B32:H32"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="B26:H26"/>
@@ -2589,14 +5389,6 @@
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="B27:H27"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2886,6 +5678,267 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="B2:B53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" ht="21" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="22" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="12"/>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="22" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="12" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="12"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="22" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="12" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="12" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="12"/>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="22" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="12" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="12" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="12" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="12"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="22" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="12" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="12" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="12" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="12" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="12" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="12" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="12" t="s">
+        <v>328</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:I52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4094,276 +7147,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B2:B53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="120" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="B2" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="12" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="12" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="12" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="12"/>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="12" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="12" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="12" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="12" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="12"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="22" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="12" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="12" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="12" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="12" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="12" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="12" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="12" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="12"/>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="22" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="12" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="12" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="12" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="12" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="12" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="12" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="12" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40" s="12" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41" s="12"/>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B42" s="22" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B43" s="12" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B44" s="12" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B45" s="12" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B46" s="12" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B47" s="12" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B48" s="12" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="12" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="12" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="12" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="12" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" s="12" t="s">
-        <v>328</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00228D31-08DB-4320-B2D6-4CC30B3DABA3}">
-  <dimension ref="A1:C324"/>
+  <dimension ref="A1:C323"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="60.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>96</v>
       </c>
@@ -4385,21 +7177,15 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Shot 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TC-01.1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tags on NB_D_STAGE.CUSTOMER_360 after the FIRST CTAS with COPY TAGS - expected ZERO PII rows because there is no predecessor table to copy from; got 'Query produced no results'. PASS - tag bootstrap gap confirmed on a real account.</t>
-        </is>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -4424,55 +7210,37 @@
         <v>109</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Shot 2</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>TC-01.2</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security gate sec-1 re-reads those tags before publishing - expected ZERO rows so the gate refuses the batch; got no results. PASS - the gate correctly blocks an untagged build.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Shot 3</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>TC-01.2</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unentitled reader reads the untagged staging table directly - expected REAL e-mail and SSN because an untagged column has nothing to mask it; got cust1@example.invalid / 001-00-0000. PASS - this is the exposure the gate exists to prevent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Shot 4</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>TC-01.2</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publish REFUSED and logged, then the thin reader views are checked - expected them still empty because no swap happened; got distinct_batches = 0, batch_seen = null. PASS (the script's EXPECT line said 1 - a documentation defect, now corrected).</t>
-        </is>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>331</v>
+      </c>
+      <c r="B47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>333</v>
+      </c>
+      <c r="B79" t="s">
+        <v>108</v>
+      </c>
+      <c r="C79" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>335</v>
+      </c>
+      <c r="B95" t="s">
+        <v>108</v>
+      </c>
+      <c r="C95" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -4497,21 +7265,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Shot 5</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>TC-01.3</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PII tags applied to CUSTOMER_360 in BOTH NB_D_LIVE and NB_D_STAGE, then rebuilt - expected 2 rows, email=EMAIL and ssn=SSN; got exactly that. PASS - seeding both schemas is the fix.</t>
-        </is>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>337</v>
+      </c>
+      <c r="B116" t="s">
+        <v>112</v>
+      </c>
+      <c r="C116" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4536,89 +7298,59 @@
         <v>117</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Shot 6</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>TC-01.4</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security gate sec-1 re-run after the fix - expected 2 rows; got 2. PASS - the gate now lets the batch through.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Shot 7</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>TC-01.4</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unentitled reader reads staging after tagging - expected ***MASKED***; got ***MASKED*** in both columns. PASS - this also closes setup assertion 6c: the masking policy really is driven by the tag.</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Shot 8</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>TC-01.4</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">After ALTER SCHEMA SWAP, batch ids across both thin reader views - expected distinct_batches = 1 and batch_seen = B1; got 1 / B1. PASS - the publish is atomic and the views are internally consistent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Shot 9</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>TC-01.4</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Approved reader NB_READER_OK through the thin view - expected real values; got cust1@example.invalid / 001-00-0000. PASS - entitlement works end to end.</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Shot 10</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>TC-01.4</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unapproved reader NB_READER_NO through the same thin view - expected ***MASKED***; got ***MASKED***. PASS - masking survives the schema swap.</t>
-        </is>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>339</v>
+      </c>
+      <c r="B153" t="s">
+        <v>116</v>
+      </c>
+      <c r="C153" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>341</v>
+      </c>
+      <c r="B174" t="s">
+        <v>116</v>
+      </c>
+      <c r="C174" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>343</v>
+      </c>
+      <c r="B192" t="s">
+        <v>116</v>
+      </c>
+      <c r="C192" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>345</v>
+      </c>
+      <c r="B213" t="s">
+        <v>116</v>
+      </c>
+      <c r="C213" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>347</v>
+      </c>
+      <c r="B232" t="s">
+        <v>116</v>
+      </c>
+      <c r="C232" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -4643,55 +7375,37 @@
         <v>122</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>Shot 11</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>TC-01.5</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Batch B2 builds into the OTHER storage, the one that was NB_D_LIVE before the swap - expected 2 rows, and ZERO would have meant only one schema was seeded; got 2. PASS - this is the check that proves the swap-pair alternation is defeated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>Shot 12</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>TC-01.5</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security gate sec-1 on batch B2 - expected 2 rows; got 2. PASS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>Shot 13</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>TC-01.5</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unentitled read of staging before the B2 swap - expected ***MASKED***; got ***MASKED***. PASS - the second storage is protected too.</t>
-        </is>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>349</v>
+      </c>
+      <c r="B255" t="s">
+        <v>120</v>
+      </c>
+      <c r="C255" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>351</v>
+      </c>
+      <c r="B280" t="s">
+        <v>120</v>
+      </c>
+      <c r="C280" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>353</v>
+      </c>
+      <c r="B301" t="s">
+        <v>120</v>
+      </c>
+      <c r="C301" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -4716,21 +7430,511 @@
         <v>126</v>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Shot 14</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>TC-01.6</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">After the second swap, batch ids across every thin reader view - expected distinct_batches = 1 and batch_seen = B2; got 1 / B2. PASS - no mixed-batch read, which is the entire requirement.</t>
-        </is>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>355</v>
+      </c>
+      <c r="B323" t="s">
+        <v>125</v>
+      </c>
+      <c r="C323" t="s">
+        <v>356</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5EA29E-B1FD-47C8-9CB8-14DF57449D6D}">
+  <dimension ref="A1:C624"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="55.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B158" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A313" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B314" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A467" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B467" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C467" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B468" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C468" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A623" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B623" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A624" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B624" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C624" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFEE8C8-A40C-492F-9F37-79A4DC5FD112}">
+  <dimension ref="A1:C242"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="62.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B173" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A242" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B242" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F2CB841-AF68-476C-ABC9-981C00319C40}">
+  <dimension ref="A1:C300"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="57.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A102" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A198" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B198" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A255" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B255" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A282" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B283" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A299" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A300" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B300" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F3A1F04-39DF-4901-836C-CC09A52CB17A}">
+  <dimension ref="A1:C237"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="54" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A175" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B175" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B237" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/w5-zone3-consumption-gating/poc07-nb/POC07_CTAS_Swap_Test_Tracker.xlsx
+++ b/w5-zone3-consumption-gating/poc07-nb/POC07_CTAS_Swap_Test_Tracker.xlsx
@@ -13,6 +13,8 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
+    <sheet name="0_Summary" sheetId="10" r:id="rId13"/>
+    <sheet name="1_Setup_Map" sheetId="11" r:id="rId14"/>
     <sheet name="1_Flow" sheetId="1" r:id="rId1"/>
     <sheet name="2_Scenarios" sheetId="3" r:id="rId2"/>
     <sheet name="5_Control_Tables" sheetId="5" r:id="rId3"/>
@@ -87,10 +89,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>CTAS into D_STAGE</t>
-  </si>
-  <si>
-    <t>CREATE OR REPLACE TABLE D_STAGE.CUSTOMER_360
+    <t>CTAS into NB_D_STAGE</t>
+  </si>
+  <si>
+    <t>CREATE OR REPLACE TABLE NB_D_STAGE.CUSTOMER_360
   COPY GRANTS COPY TAGS
   AS SELECT * FROM V_CUSTOMER_360</t>
   </si>
@@ -131,7 +133,7 @@
     <t>SWAP</t>
   </si>
   <si>
-    <t>ALTER SCHEMA D_STAGE SWAP WITH D_LIVE
+    <t>ALTER SCHEMA NB_D_STAGE SWAP WITH NB_D_LIVE
 one metadata operation — no data moves</t>
   </si>
   <si>
@@ -144,7 +146,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>D_LIVE</t>
+    <t>NB_D_LIVE</t>
   </si>
   <si>
     <t>the published tables</t>
@@ -156,10 +158,10 @@
     <t>8</t>
   </si>
   <si>
-    <t>D_VIEWS.V_*</t>
-  </si>
-  <si>
-    <t>thin reader views —  SELECT * FROM D_LIVE.CUSTOMER_360
+    <t>NB_D_VIEWS.V_*</t>
+  </si>
+  <si>
+    <t>thin reader views —  SELECT * FROM NB_D_LIVE.CUSTOMER_360
 no logic, stable name</t>
   </si>
   <si>
@@ -178,22 +180,22 @@
     <t>Z3_CONSUME.V_CUSTOMER_360      source view, complex logic        build time only</t>
   </si>
   <si>
-    <t>D_LIVE.CUSTOMER_360            published table                   the CTAS target</t>
-  </si>
-  <si>
-    <t>D_VIEWS.V_CUSTOMER_360         thin reader view                  what Power BI reads</t>
+    <t>NB_D_LIVE.CUSTOMER_360            published table                   the CTAS target</t>
+  </si>
+  <si>
+    <t>NB_D_VIEWS.V_CUSTOMER_360         thin reader view                  what Power BI reads</t>
   </si>
   <si>
     <t>Why there are three schemas</t>
   </si>
   <si>
-    <t>D_STAGE  and  D_LIVE   exchange identities at every swap — so staging must be PERMANENT, it becomes live</t>
-  </si>
-  <si>
-    <t>D_VIEWS                sits OUTSIDE the swap, or the reader views would be swapped out with the tables</t>
-  </si>
-  <si>
-    <t>CTRL                   sits OUTSIDE the swap, or the procedure would lose its own state mid-run</t>
+    <t>NB_D_STAGE  and  NB_D_LIVE   exchange identities at every swap — so staging must be PERMANENT, it becomes live</t>
+  </si>
+  <si>
+    <t>NB_D_VIEWS                sits OUTSIDE the swap, or the reader views would be swapped out with the tables</t>
+  </si>
+  <si>
+    <t>NB_CTRL                   sits OUTSIDE the swap, or the procedure would lose its own state mid-run</t>
   </si>
   <si>
     <t>Scenarios — each one starts fresh on day 1</t>
@@ -358,7 +360,7 @@
     <t>B1</t>
   </si>
   <si>
-    <t>Deploy D_LIVE and D_STAGE with the published table created in BOTH, but with NO tags applied. Run the first CTAS with COPY TAGS into D_STAGE.</t>
+    <t>Deploy NB_D_LIVE and NB_D_STAGE with the published table created in BOTH, but with NO tags applied. Run the first CTAS with COPY TAGS into NB_D_STAGE.</t>
   </si>
   <si>
     <t>RECORD — expected: the staging table has NO tags. COPY TAGS has no predecessor to copy from.</t>
@@ -373,7 +375,7 @@
     <t>Run the security check against that untagged staging table, and read a sensitive column as an unapproved reader.</t>
   </si>
   <si>
-    <t>REFUSED. The column reads as plaintext in staging, the check refuses, no swap happens, D_LIVE is unchanged.</t>
+    <t>REFUSED. The column reads as plaintext in staging, the check refuses, no swap happens, NB_D_LIVE is unchanged.</t>
   </si>
   <si>
     <t>Check output + the reader's query result + PUBLISH_LOG row</t>
@@ -382,7 +384,7 @@
     <t>TC-01.3</t>
   </si>
   <si>
-    <t>Apply the PII tags to the table in BOTH D_LIVE and D_STAGE. Re-run the CTAS with COPY TAGS.</t>
+    <t>Apply the PII tags to the table in BOTH NB_D_LIVE and NB_D_STAGE. Re-run the CTAS with COPY TAGS.</t>
   </si>
   <si>
     <t>PASS — the staging table now carries its tags.</t>
@@ -493,7 +495,7 @@
     <t>TC-03.1</t>
   </si>
   <si>
-    <t>Seed the tags in D_LIVE ONLY, not in D_STAGE. Publish four consecutive batches, recording the published table's tags after each.</t>
+    <t>Seed the tags in NB_D_LIVE ONLY, not in NB_D_STAGE. Publish four consecutive batches, recording the published table's tags after each.</t>
   </si>
   <si>
     <t>RECORD — expected: tags alternate present / absent. This is the failure mode when a new object is added to one schema only.</t>
@@ -610,7 +612,7 @@
     <t>TC-04.7</t>
   </si>
   <si>
-    <t>As the VIEW OWNER role, read a sensitive column in D_STAGE after the rebuild and before the swap.</t>
+    <t>As the VIEW OWNER role, read a sensitive column in NB_D_STAGE after the rebuild and before the swap.</t>
   </si>
   <si>
     <t>RECORD — can the view owner read staging? This is the cost of the future-grant rule; COPY GRANTS passing in TC-04.3 would remove it.</t>
@@ -634,7 +636,7 @@
     <t>Mark one REQUIRED dependency FAILED. Publish.</t>
   </si>
   <si>
-    <t>REFUSED — the log names the blocking object; D_LIVE still shows B1.</t>
+    <t>REFUSED — the log names the blocking object; NB_D_LIVE still shows B1.</t>
   </si>
   <si>
     <t>Gate query + log + reader check</t>
@@ -724,7 +726,7 @@
     <t>Rename one source view (ALTER VIEW ... RENAME TO ..._BROKEN) so its CTAS fails. Run the publish.</t>
   </si>
   <si>
-    <t>REFUSED — that table's BATCH_STATUS is FAILED, the others COMPLETED. No swap. D_LIVE still shows B1.</t>
+    <t>REFUSED — that table's BATCH_STATUS is FAILED, the others COMPLETED. No swap. NB_D_LIVE still shows B1.</t>
   </si>
   <si>
     <t>BATCH_STATUS + log + reader check</t>
@@ -793,10 +795,10 @@
     <t>TC-08.3</t>
   </si>
   <si>
-    <t>A reader queries D_LIVE and D_STAGE directly.</t>
-  </si>
-  <si>
-    <t>PASS — denied on both. Readers hold SELECT on D_VIEWS only.</t>
+    <t>A reader queries NB_D_LIVE and NB_D_STAGE directly.</t>
+  </si>
+  <si>
+    <t>PASS — denied on both. Readers hold SELECT on NB_D_VIEWS only.</t>
   </si>
   <si>
     <t>Both error messages</t>
@@ -910,7 +912,7 @@
     <t>-- DEFINITION — static, deployed once, one row per object</t>
   </si>
   <si>
-    <t>CREATE TABLE CTRL.OBJECT_REGISTRY (</t>
+    <t>CREATE TABLE NB_CTRL.OBJECT_REGISTRY (</t>
   </si>
   <si>
     <t xml:space="preserve">    object_name     STRING,        -- CUSTOMER_360   (built from V_CUSTOMER_360)</t>
@@ -922,10 +924,10 @@
     <t xml:space="preserve">    is_required     STRING DEFAULT 'Y',</t>
   </si>
   <si>
-    <t xml:space="preserve">    live_schema     STRING,        -- D_LIVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    stage_schema    STRING         -- D_STAGE</t>
+    <t xml:space="preserve">    live_schema     STRING,        -- NB_D_LIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    stage_schema    STRING         -- NB_D_STAGE</t>
   </si>
   <si>
     <t>);</t>
@@ -934,7 +936,7 @@
     <t>-- DEFINITION — the dependency edge list.  Zone 3 objects only</t>
   </si>
   <si>
-    <t>CREATE TABLE CTRL.OBJECT_DEPENDENCY (</t>
+    <t>CREATE TABLE NB_CTRL.OBJECT_DEPENDENCY (</t>
   </si>
   <si>
     <t xml:space="preserve">    object_name       STRING,</t>
@@ -946,7 +948,7 @@
     <t>-- STATE — one row per object per batch.  Covers source loads AND rebuilds</t>
   </si>
   <si>
-    <t>CREATE TABLE CTRL.BATCH_STATUS (</t>
+    <t>CREATE TABLE NB_CTRL.BATCH_STATUS (</t>
   </si>
   <si>
     <t xml:space="preserve">    batch_id        STRING,</t>
@@ -976,7 +978,7 @@
     <t>-- EVIDENCE — one row per publish attempt</t>
   </si>
   <si>
-    <t>CREATE TABLE CTRL.PUBLISH_LOG (</t>
+    <t>CREATE TABLE NB_CTRL.PUBLISH_LOG (</t>
   </si>
   <si>
     <t xml:space="preserve">    attempted_at    TIMESTAMP_NTZ,</t>
@@ -1006,13 +1008,13 @@
     <t xml:space="preserve">       s.status</t>
   </si>
   <si>
-    <t>FROM      CTRL.OBJECT_REGISTRY   r</t>
-  </si>
-  <si>
-    <t>JOIN      CTRL.OBJECT_DEPENDENCY d ON d.object_name = r.object_name</t>
-  </si>
-  <si>
-    <t>LEFT JOIN CTRL.BATCH_STATUS      s ON s.object_name = d.depends_on_object</t>
+    <t>FROM      NB_CTRL.OBJECT_REGISTRY   r</t>
+  </si>
+  <si>
+    <t>JOIN      NB_CTRL.OBJECT_DEPENDENCY d ON d.object_name = r.object_name</t>
+  </si>
+  <si>
+    <t>LEFT JOIN NB_CTRL.BATCH_STATUS      s ON s.object_name = d.depends_on_object</t>
   </si>
   <si>
     <t xml:space="preserve">                                  AND s.batch_id    = :B</t>
@@ -5394,6 +5396,1812 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POC07 — CTAS + Swap · test results</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scenarios S01–S05 executed on LM_POC_DB / POC_WH. 75 screenshots validated against the scripts. S06–S10 not yet run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scen</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test case</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What it proves</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Expected</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actual</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verdict</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-01.1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COPY TAGS on a first build has no predecessor</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zero PII tags on staging</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zero</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-01.2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The security gate refuses an untagged build</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zero tags; unentitled reader sees REAL values; nothing published</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as expected; views stayed empty</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-01.3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tagging the table in BOTH schemas fixes it</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 tags after rebuild</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-01.4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gate passes, swap publishes, masking holds</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 tags; masked for unentitled; 1 / B1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as expected</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-01.5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fix survives the swap-pair alternation</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 tags on the OTHER storage</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-01.6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One batch id across every reader view</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 / B2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 / B2</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baseline publish of B1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 tags, 3 grants, 1 / B1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as expected</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2 repeats with no drift</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">identical to baseline</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">identical</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B3 repeats with no drift</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">identical to baseline</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">identical</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B4 repeats with no drift</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">identical to baseline</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">identical</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Four batches, no cumulative drift</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 PUBLISHED rows; final tags = baseline</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 PUBLISHED; tags identical</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seeding ONE schema loses tags on alternate batches</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tags only on batches landing in the seeded storage</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B1=0, B2=2, B3=0, B4=2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUST REPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Does COPY TAGS carry a TABLE-level tag?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">record the outcome</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PII_SCOPE=NB_OVERRIDE survived</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A renamed column loses its tag</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">renamed column untagged, ssn still tagged</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zero rows — nothing was tagged going in</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INCONCLUSIVE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-run after fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A newly tagged base column arrives unprotected</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phone untagged on the published table</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phone untagged; REAL phone numbers readable</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUST REPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The swap carries grants with the storage</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROBE keeps SELECT across the swap</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kept</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A plain CTAS drops grants</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROBE SELECT gone</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gone</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COPY GRANTS keeps them</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROBE keeps SELECT</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kept — all 3 grants</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">…and the tags alongside</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 tag rows</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO — TC-04.2 stripped this storage and COPY TAGS copied an untagged predecessor</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAIL</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Script defect, fixed; re-run</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stable across a further batch and the other storage</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grants unchanged, 2 tags</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unchanged; 2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COPY GRANTS cannot bootstrap either</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no grants copied on a first build</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROBE absent</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUST REPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COPY GRANTS does not move OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner can still swap both schemas</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_PUBLISH_ROLE</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.7</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Can the view owner read staging?</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">record access and masking</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">read succeeded, REAL values — but due to the TC-04.3 tag loss</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INCONCLUSIVE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-run after fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All dependencies COMPLETED publishes</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gate empty; 1 / B1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as expected</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A required dependency FAILED is refused</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gate names the blocker; views stay at B1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 blocked rows; 1 / B1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A MISSING status row is also refused</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gate shows NO STATUS ROW; views stay at B1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 rows NO STATUS ROW; 1 / B1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A non-required failure does NOT block</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gate empty; 1 / B4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as expected</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Totals</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS 23   ·   FAIL 1   ·   INCONCLUSIVE 2   ·   26 test cases across S01–S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Findings that go in the report whatever else happens</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tag bootstrap gap is real. The first CTAS with COPY TAGS produced an untagged table and an unentitled reader saw real e-mail and SSN. (S01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seeding one schema is NOT enough. Tags alternate 0,2,0,2 across batches — the loss repeats forever, not just on day 1. Deploy tagged in BOTH schemas. (S03 TC-03.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COPY GRANTS works and removes the need for future grants on the swap schemas — but it cannot bootstrap either. (S04 TC-04.3 / TC-04.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A newly tagged Zone 3 base column reaches the published table UNPROTECTED. Adding a PII column needs its own deployment step. (S03 TC-03.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A plain CTAS without COPY TAGS un-protects the table, and a later COPY TAGS cannot recover it — it copies from the now-untagged predecessor. (S04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The dependency gate behaves correctly on all four cases, including a missing status row, which is treated as not-completed rather than success. (S05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open items</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S03 TC-03.3 and S04 TC-04.3/04.7 need a re-run: the scripts have been fixed so each case starts from a properly tagged table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S06 to S10 not yet executed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D55"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="62" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What 00_setup.sql built, and how a scenario runs against it</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Database LM_POC_DB (SHARED — the colleague's POC schemas also live here) · warehouse POC_WH · everything we own is named NB_</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schema</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holds</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Owner</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In the swap?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_BASE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CUSTOMER, POLICY — what the "ETL" loads each batch</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_BASE_OWNER</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_SRC_VIEWS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V_CUSTOMER_360, V_POLICY_SUMMARY — the existing complex logic</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_BASE_OWNER</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_GOV</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tag PII, tag PII_SCOPE, policy MASK_PII, ENTITLEMENT table</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYSADMIN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_D_STAGE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where the next batch is built</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_PUBLISH_ROLE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_D_LIVE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the published tables</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_PUBLISH_ROLE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_D_VIEWS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V_CUSTOMER_360, V_POLICY_SUMMARY — thin reader views</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_VIEW_OWNER</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_CTRL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBJECT_REGISTRY, OBJECT_DEPENDENCY, BATCH_STATUS, PUBLISH_LOG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_PUBLISH_ROLE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What it is</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entitled to see PII?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_BASE_OWNER</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owns the base tables and the source views</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_PUBLISH_ROLE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">builds and swaps. MUST be entitled, or the CTAS writes masks into the table</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_VIEW_OWNER</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owns the thin views. Deliberately NOT entitled</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_READER_OK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">an approved report user</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_READER_NO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">an unapproved report user</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_PROBE_ROLE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grant target, so S04 can watch a grant survive or vanish</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_BATCH_NOENT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a batch identity with no entitlement — proves a writer stores masks</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How one batch flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What happens</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible to reports?</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_BASE.CUSTOMER / POLICY</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the "ETL" loads this batch and writes COMPLETED or FAILED to NB_CTRL.BATCH_STATUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_SRC_VIEWS.V_*</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">existing complex logic, unchanged — build-time source only</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CTAS into NB_D_STAGE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CREATE OR REPLACE TABLE NB_D_STAGE.CUSTOMER_360 COPY GRANTS COPY TAGS AS SELECT * FROM NB_SRC_VIEWS.V_CUSTOMER_360</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dependency gate</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">join OBJECT_REGISTRY + OBJECT_DEPENDENCY + BATCH_STATUS. ANY row returned = do not publish</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security gate</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">are the PII tags on the staging table, and does an unentitled role read masks?</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWAP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTER SCHEMA NB_D_STAGE SWAP WITH NB_D_LIVE — one metadata operation, no data moves</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;- THE MOMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_D_LIVE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the published tables</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_D_VIEWS.V_*</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thin reader views, stable names — SELECT * FROM NB_D_LIVE.CUSTOMER_360</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power BI</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reports</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The one thing to understand: the swap pair ALTERNATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NB_D_LIVE and NB_D_STAGE exchange their physical storage at every swap. The names stay put; the storage moves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">So there are TWO storages, each with its own tag and grant lineage, and each one is rebuilt every OTHER batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anything deployed to only one of them (a tag, a grant) is therefore missing on half of all batches — forever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S03 TC-03.1 measures exactly this and returned 0, 2, 0, 2 across four batches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How a scenario script is run</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run 00_setup.sql ONCE. Then any scenario, in any order — each one resets the swap pair, the reader views and the control tables back to day 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run each file top to bottom in ONE Snowsight worksheet session: the scripts switch roles constantly and use SHOW + RESULT_SCAN pairs that return the wrong answer, not an error, if anything runs in between.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Three statements are MEANT to fail (s07 TC-07.2, s08 TC-08.3, s04 TC-04.5). Capture the error — the error is the result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99_teardown.sql drops our seven NB_ schemas BY NAME and the seven NB_ roles. It never drops LM_POC_DB.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:H14"/>
@@ -7449,7 +9257,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5EA29E-B1FD-47C8-9CB8-14DF57449D6D}">
-  <dimension ref="A1:C624"/>
+  <dimension ref="A1:C644"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="55.42578125" customWidth="1"/>
@@ -7477,6 +9285,108 @@
         <v>130</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dependency gate for B1 with every required dependency COMPLETED - expected zero blocking rows; got none, so the batch may publish. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tags on staging after the B1 CTAS - expected 2 rows, email=EMAIL and ssn=SSN; got 2. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 3</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unentitled reader on staging before the swap - expected ***MASKED***; got masked in both columns. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 4</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch ids across the thin views after the swap - expected distinct_batches = 1 and batch_seen = B1; got 1 / B1. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 5</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tags on the PUBLISHED table after B1, the baseline for the whole scenario - expected 2 rows; got 2. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 6</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.1</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants on the published table after B1, the grant baseline - expected PROBE SELECT, PUBLISH OWNERSHIP, VIEW_OWNER SELECT; got all 3. PASS.</t>
+        </is>
+      </c>
+    </row>
     <row r="157" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>96</v>
@@ -7499,6 +9409,108 @@
         <v>134</v>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 7</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.2</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dependency gate for B2 - expected zero blocking rows; got none. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 8</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.2</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tags on staging after the B2 CTAS - expected 2 rows; got 2. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 9</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.2</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unentitled reader on staging - expected ***MASKED***; got masked. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 10</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.2</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch ids after the B2 swap - expected 1 / B2; got 1 / B2. PASS - no mixed batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 11</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.2</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Published tags after B2 - expected identical to the B1 baseline; got 2 rows, unchanged. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 12</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.2</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Published grants after B2 - expected identical to the B1 baseline; got all 3, unchanged. PASS.</t>
+        </is>
+      </c>
+    </row>
     <row r="313" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
         <v>96</v>
@@ -7521,6 +9533,108 @@
         <v>139</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 13</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.3</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dependency gate for B3 - expected zero blocking rows; got none. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 14</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.3</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tags on staging after the B3 CTAS - expected 2 rows; got 2. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 15</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.3</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unentitled reader on staging - expected ***MASKED***; got masked. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 16</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.3</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch ids after the B3 swap - expected 1 / B3; got 1 / B3. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 17</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.3</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Published tags after B3 - expected unchanged; got 2 rows. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 18</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.3</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Published grants after B3 - expected unchanged; got all 3. PASS.</t>
+        </is>
+      </c>
+    </row>
     <row r="467" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
         <v>96</v>
@@ -7543,6 +9657,108 @@
         <v>143</v>
       </c>
     </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 19</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.4</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dependency gate for B4 - expected zero blocking rows; got none. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 20</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.4</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tags on staging after the B4 CTAS - expected 2 rows; got 2. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 21</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.4</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unentitled reader on staging - expected ***MASKED***; got masked. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 22</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.4</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch ids after the B4 swap - expected 1 / B4; got 1 / B4. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 23</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.4</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Published tags after B4 - expected unchanged; got 2 rows. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 24</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.4</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Published grants after B4 - expected unchanged; got all 3. PASS.</t>
+        </is>
+      </c>
+    </row>
     <row r="623" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A623" s="3" t="s">
         <v>96</v>
@@ -7563,6 +9779,40 @@
       </c>
       <c r="C624" s="5" t="s">
         <v>146</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 25</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.5</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publish history across the scenario - expected four PUBLISHED rows B1 to B4; got exactly four, all PUBLISHED by NB_PUBLISH_ROLE. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 26</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-02.5</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Final tag state compared with the TC-02.1 baseline - expected identical; got the same 2 rows. PASS - ZERO DRIFT across four rebuilds and four swaps.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7573,7 +9823,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFEE8C8-A40C-492F-9F37-79A4DC5FD112}">
-  <dimension ref="A1:C242"/>
+  <dimension ref="A1:C274"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="62.85546875" customWidth="1"/>
@@ -7601,6 +9851,91 @@
         <v>150</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch B1 staging tags, with the PII tags seeded in NB_D_LIVE ONLY - B1 builds into the UNSEEDED storage, so expected zero; got zero. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch B2 - the swap has brought the SEEDED storage into staging, so expected 2 rows; got 2. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch B3 - back on the unseeded storage, expected zero; got zero. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 4</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch B4 - seeded storage again, expected 2; got 2. PASS. ** HEADLINE FINDING: the sequence is 0, 2, 0, 2 - seeding only one schema loses the tags on EVERY OTHER BATCH, permanently, not just on the first build. **</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 5</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publish log for the four batches - all four recorded PUBLISHED, including B1 and B3 which carried no tags at all. RECORD: without the security gate the tag loss publishes silently.</t>
+        </is>
+      </c>
+    </row>
     <row r="130" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>96</v>
@@ -7623,6 +9958,40 @@
         <v>154</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 6</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.2</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Table-level PII_SCOPE = NB_OVERRIDE applied to the staging table before the rebuild - expected that value present; got it. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 7</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.2</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The same table tag read back AFTER a COPY GRANTS COPY TAGS rebuild - expected to establish whether it survives; it DID. PASS - COPY TAGS carries TABLE-level tags, not only column-level ones.</t>
+        </is>
+      </c>
+    </row>
     <row r="172" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>96</v>
@@ -7645,6 +10014,40 @@
         <v>158</v>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 8</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.3</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tags after renaming email to email_address in the source view - expected the renamed column untagged but ssn still tagged; got ZERO rows. INCONCLUSIVE, not a failure: TC-03.1 left the unseeded storage in NB_D_STAGE, so there were no column tags to lose. Needs a re-run after the script fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 9</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.3</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security check sec-1 on the same rebuild - zero rows, same cause as above. INCONCLUSIVE - re-run required.</t>
+        </is>
+      </c>
+    </row>
     <row r="241" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>96</v>
@@ -7665,6 +10068,40 @@
       </c>
       <c r="C242" s="5" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 10</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.4</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tags after adding a NEWLY TAGGED base column (phone) and including it in the view - expected phone to arrive UNTAGGED on the published table; got zero PII rows. PASS on mechanism: COPY TAGS copies from the predecessor table, which never had a phone column to copy a tag from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 11</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-03.4</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unentitled read of that new column - expected to record whether real values appear; got REAL phone numbers (+44-0000-1). PASS - a newly tagged Zone 3 base column reaches the published table completely unprotected.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7675,7 +10112,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F2CB841-AF68-476C-ABC9-981C00319C40}">
-  <dimension ref="A1:C300"/>
+  <dimension ref="A1:C303"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="57.7109375" customWidth="1"/>
@@ -7703,6 +10140,40 @@
         <v>166</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants on the staging table BEFORE the swap - expected NB_PROBE_ROLE to hold SELECT; got 3 rows including PROBE. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The same grants read on NB_D_LIVE AFTER the swap - same storage, new name - expected PROBE to still hold SELECT; got all 3 unchanged. PASS - the swap carries grants with the storage.</t>
+        </is>
+      </c>
+    </row>
     <row r="50" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>96</v>
@@ -7725,6 +10196,40 @@
         <v>170</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 3</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants immediately before a deliberate plain rebuild - 3 rows including PROBE. Baseline for the next shot. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 4</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants after CREATE OR REPLACE with NO COPY GRANTS - expected PROBE SELECT to be GONE; got 2 rows, PROBE absent. PASS - a plain CTAS drops grants. (NB_VIEW_OWNER survives on a future grant left behind by an earlier scenario.)</t>
+        </is>
+      </c>
+    </row>
     <row r="101" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>96</v>
@@ -7747,6 +10252,57 @@
         <v>174</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 5</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.3</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants after a CREATE OR REPLACE ... COPY GRANTS COPY TAGS rebuild - expected PROBE to still hold SELECT; got all 3 back. PASS - KEY RESULT: COPY GRANTS preserves grants, so future grants on the swap schemas are not required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 6</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.3</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security check sec-1 on the same table - expected 2 tag rows; got ZERO. FAIL against the written expectation. Cause: TC-04.2 stripped this storage tags with its deliberate plain rebuild and COPY TAGS then copied from an untagged predecessor. Script defect, now fixed; re-run required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 7</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.3</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch ids after the swap - expected 1 / B2; got 1 / B2. PASS.</t>
+        </is>
+      </c>
+    </row>
     <row r="197" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>96</v>
@@ -7769,6 +10325,40 @@
         <v>178</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 8</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.4</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tags on staging for batch B3 - expected 2 rows; got 2, because the swap brought the still-tagged storage back into staging. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 9</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.4</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants after B3 - expected unchanged with no future grants in play; got all 3. PASS - COPY GRANTS holds across a further batch AND across the other storage.</t>
+        </is>
+      </c>
+    </row>
     <row r="254" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
         <v>96</v>
@@ -7791,6 +10381,23 @@
         <v>182</v>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 10</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.5</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants on a FIRST build with COPY GRANTS, the table having been dropped - expected nothing copied; NB_PROBE_ROLE is ABSENT. PASS - the GRANT BOOTSTRAP GAP, exactly mirroring the tag bootstrap gap in S01. (NB_VIEW_OWNER row is a leftover future grant, not a copy.)</t>
+        </is>
+      </c>
+    </row>
     <row r="282" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
         <v>96</v>
@@ -7813,6 +10420,23 @@
         <v>185</v>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 11</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.6</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Owner of the published table after a COPY GRANTS rebuild - expected a role that can still swap both schemas; got NB_PUBLISH_ROLE. PASS - COPY GRANTS does not carry OWNERSHIP, and ownership stayed where it belongs.</t>
+        </is>
+      </c>
+    </row>
     <row r="299" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
         <v>96</v>
@@ -7833,6 +10457,23 @@
       </c>
       <c r="C300" s="5" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 12</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-04.7</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">View owner reading a sensitive column in staging - the read SUCCEEDS and returns REAL email and SSN. Exposure is real, but on this run it follows from the TC-04.2 tag strip above rather than from the view owner privilege alone. INCONCLUSIVE - re-run after the script fix.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7843,7 +10484,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F3A1F04-39DF-4901-836C-CC09A52CB17A}">
-  <dimension ref="A1:C237"/>
+  <dimension ref="A1:C320"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="54" customWidth="1"/>
@@ -7871,6 +10512,74 @@
         <v>192</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dependency gate for B1 with every required dependency COMPLETED - expected zero blocking rows; got none. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tags on staging - expected 2 rows; got 2. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 3</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unentitled reader on staging - expected ***MASKED***; got masked. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 4</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch ids after the swap - expected 1 / B1; got 1 / B1. PASS.</t>
+        </is>
+      </c>
+    </row>
     <row r="110" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>96</v>
@@ -7893,6 +10602,40 @@
         <v>196</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 5</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.2</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dependency gate for B2 with POLICY reported FAILED - expected 2 rows, CUSTOMER_360 and POLICY_SUMMARY both blocked by POLICY; got exactly that with status FAILED. PASS - the gate refuses the publish.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 6</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.2</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch ids after that refusal - expected 1 / B1 because the failed batch published nothing; got 1 / B1. PASS. (The script also carried a stale generic line saying B2 - a documentation defect, now corrected.)</t>
+        </is>
+      </c>
+    </row>
     <row r="174" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>96</v>
@@ -7915,6 +10658,40 @@
         <v>200</v>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 7</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.3</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dependency gate for B3 where POLICY has NO status row at all - expected 2 rows showing NO STATUS ROW; got exactly that. PASS - a missing row is treated as not-completed, never as success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 8</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.3</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch ids after that refusal - expected 1 / B1; got 1 / B1. PASS. (Same stale generic line, now corrected.)</t>
+        </is>
+      </c>
+    </row>
     <row r="236" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>96</v>
@@ -7935,6 +10712,74 @@
       </c>
       <c r="C237" s="5" t="s">
         <v>204</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 9</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.4</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dependency gate for B4 where POLICY is FAILED but the dependent published table is marked is_required = N - expected zero blocking rows; got none. PASS - a non-required failure does not block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 10</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.4</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tags on staging - expected 2 rows; got 2. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 11</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.4</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unentitled reader on staging - expected ***MASKED***; got masked. PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shot 12</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-05.4</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch ids after the swap - expected 1 / B4; got 1 / B4. PASS - the publish went ahead despite a non-required dependency failing.</t>
+        </is>
       </c>
     </row>
   </sheetData>
